--- a/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2022_T3_0.xlsx
+++ b/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2022_T3_0.xlsx
@@ -57,7 +57,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>57</t>
+    <t>51</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -69,40 +69,40 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>20.957</t>
-  </si>
-  <si>
-    <t>(19.470)</t>
-  </si>
-  <si>
-    <t>6.579</t>
-  </si>
-  <si>
-    <t>(1.035)</t>
-  </si>
-  <si>
-    <t>2.334</t>
-  </si>
-  <si>
-    <t>(0.633)</t>
-  </si>
-  <si>
-    <t>36.357</t>
-  </si>
-  <si>
-    <t>(29.154)</t>
-  </si>
-  <si>
-    <t>2.570</t>
-  </si>
-  <si>
-    <t>(0.634)</t>
-  </si>
-  <si>
-    <t>11.000</t>
-  </si>
-  <si>
-    <t>(1.429)</t>
+    <t>1.352</t>
+  </si>
+  <si>
+    <t>(0.282)</t>
+  </si>
+  <si>
+    <t>7.176</t>
+  </si>
+  <si>
+    <t>(1.124)</t>
+  </si>
+  <si>
+    <t>2.141</t>
+  </si>
+  <si>
+    <t>(0.572)</t>
+  </si>
+  <si>
+    <t>6.940</t>
+  </si>
+  <si>
+    <t>(1.541)</t>
+  </si>
+  <si>
+    <t>2.629</t>
+  </si>
+  <si>
+    <t>(0.680)</t>
+  </si>
+  <si>
+    <t>12.235</t>
+  </si>
+  <si>
+    <t>(1.504)</t>
   </si>
   <si>
     <t>0.000</t>
@@ -111,22 +111,22 @@
     <t>(0.000)</t>
   </si>
   <si>
-    <t>10.496</t>
-  </si>
-  <si>
-    <t>(9.739)</t>
-  </si>
-  <si>
-    <t>142.752</t>
-  </si>
-  <si>
-    <t>(131.399)</t>
-  </si>
-  <si>
-    <t>3.099</t>
-  </si>
-  <si>
-    <t>(0.894)</t>
+    <t>0.818</t>
+  </si>
+  <si>
+    <t>(0.389)</t>
+  </si>
+  <si>
+    <t>11.300</t>
+  </si>
+  <si>
+    <t>(2.373)</t>
+  </si>
+  <si>
+    <t>2.724</t>
+  </si>
+  <si>
+    <t>(0.752)</t>
   </si>
   <si>
     <t>59</t>
@@ -192,7 +192,7 @@
     <t>(0.658)</t>
   </si>
   <si>
-    <t>116</t>
+    <t>110</t>
   </si>
   <si>
     <t>.n</t>
@@ -207,31 +207,31 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>-19.507</t>
-  </si>
-  <si>
-    <t>3.014*</t>
-  </si>
-  <si>
-    <t>2.228**</t>
-  </si>
-  <si>
-    <t>-28.228</t>
-  </si>
-  <si>
-    <t>-0.890</t>
-  </si>
-  <si>
-    <t>-0.102</t>
-  </si>
-  <si>
-    <t>-10.060</t>
-  </si>
-  <si>
-    <t>-130.771</t>
-  </si>
-  <si>
-    <t>1.367</t>
+    <t>0.097</t>
+  </si>
+  <si>
+    <t>2.417</t>
+  </si>
+  <si>
+    <t>2.421**</t>
+  </si>
+  <si>
+    <t>1.189</t>
+  </si>
+  <si>
+    <t>-0.948</t>
+  </si>
+  <si>
+    <t>-1.337</t>
+  </si>
+  <si>
+    <t>-0.381</t>
+  </si>
+  <si>
+    <t>0.680</t>
+  </si>
+  <si>
+    <t>1.742*</t>
   </si>
 </sst>
 </file>
